--- a/categories_index.xlsx
+++ b/categories_index.xlsx
@@ -434,22 +434,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
@@ -900,29 +900,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
@@ -1338,6 +1338,13 @@
       <c r="A60" t="inlineStr">
         <is>
           <t>6703 Payroll Taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>62000 Business Licenses and Taxes</t>
         </is>
       </c>
     </row>

--- a/categories_index.xlsx
+++ b/categories_index.xlsx
@@ -4,22 +4,96 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
   </bookViews>
   <sheets>
-    <sheet name="wages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="pr_taxes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="pr_fees" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="subscriptions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="utilities" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="wages" sheetId="1" r:id="rId1" state="visible"/>
+    <sheet name="pr_taxes" sheetId="2" r:id="rId2" state="visible"/>
+    <sheet name="pr_fees" sheetId="3" r:id="rId3" state="visible"/>
+    <sheet name="subscriptions" sheetId="4" r:id="rId4" state="visible"/>
+    <sheet name="utilities" sheetId="5" r:id="rId5" state="visible"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>5150 Direct Labor - Bonus</t>
+  </si>
+  <si>
+    <t>5150 Direct Labor - Bonuses</t>
+  </si>
+  <si>
+    <t>1-65520 Bonuses</t>
+  </si>
+  <si>
+    <t>2401 Accrued Bonuses</t>
+  </si>
+  <si>
+    <t>3-65520 Bonuses</t>
+  </si>
+  <si>
+    <t>5023 DL - Bonus</t>
+  </si>
+  <si>
+    <t>60005 Bonus</t>
+  </si>
+  <si>
+    <t>60006 Bonus</t>
+  </si>
+  <si>
+    <t>6004 Employee Bonus</t>
+  </si>
+  <si>
+    <t>60040 Bonus</t>
+  </si>
+  <si>
+    <t>60050 Bonus</t>
+  </si>
+  <si>
+    <t>6009 Bonus</t>
+  </si>
+  <si>
+    <t>6023 Employee Bonus</t>
+  </si>
+  <si>
+    <t>6024 Employee PR - Bonuses</t>
+  </si>
+  <si>
+    <t>6025 Employee Bonuses</t>
+  </si>
+  <si>
+    <t>6111 Employee PR - Bonus</t>
+  </si>
+  <si>
+    <t>6359 Margin Bonus</t>
+  </si>
+  <si>
+    <t>6361 Bonus &amp; Incentives</t>
+  </si>
+  <si>
+    <t>6404 Employee Bonus</t>
+  </si>
+  <si>
+    <t>64500 Bonus</t>
+  </si>
+  <si>
+    <t>6555 Bonus</t>
+  </si>
+  <si>
+    <t>6709 Bonus</t>
+  </si>
+  <si>
+    <t>60002 Officer Bonus</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="0"/>
   <fonts count="2">
     <font>
@@ -60,13 +134,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -139,7 +213,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -422,15 +496,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -887,6 +961,121 @@
         <is>
           <t>6701 Salaries &amp; Wages</t>
         </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/categories_index.xlsx
+++ b/categories_index.xlsx
@@ -535,6 +535,9 @@
           <t>1-22800 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -542,6 +545,9 @@
           <t>1-65530 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -549,6 +555,9 @@
           <t>1-65540 Tech Salaries</t>
         </is>
       </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,6 +565,9 @@
           <t>21102 Contractor Wages P...</t>
         </is>
       </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -563,6 +575,9 @@
           <t>2200 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -570,6 +585,9 @@
           <t>2200 Wages Payable</t>
         </is>
       </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -577,6 +595,9 @@
           <t>22000 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -584,6 +605,9 @@
           <t>22000 Wages Payable</t>
         </is>
       </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -591,6 +615,9 @@
           <t>2201 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -598,6 +625,9 @@
           <t>22010 Salaries &amp; Wages Payable</t>
         </is>
       </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -605,6 +635,9 @@
           <t>2210 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -612,6 +645,9 @@
           <t>2215 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -619,6 +655,9 @@
           <t>2310 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -626,6 +665,9 @@
           <t>2400 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -633,6 +675,9 @@
           <t>24000 Payroll Liabilities</t>
         </is>
       </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -640,6 +685,9 @@
           <t>3-65530 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -647,6 +695,9 @@
           <t>4-65530 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -654,6 +705,9 @@
           <t>5001 Direct Labor - Wages</t>
         </is>
       </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -661,6 +715,9 @@
           <t>5001 Direct Labor Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -668,6 +725,9 @@
           <t>5001 Direct Wages</t>
         </is>
       </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -675,6 +735,9 @@
           <t>50063 Fulfillment Center Wages</t>
         </is>
       </c>
+      <c r="B22">
+        <v>15</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -682,6 +745,9 @@
           <t>5021 DL - EE Wages</t>
         </is>
       </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -689,6 +755,9 @@
           <t>5021 Employee PR - DL Wages</t>
         </is>
       </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -696,6 +765,9 @@
           <t>5100 Direct Salaries &amp; Benefits</t>
         </is>
       </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -703,6 +775,9 @@
           <t>5101 Direct Labor PR - Wages</t>
         </is>
       </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -710,6 +785,9 @@
           <t>5101 Direct Wages</t>
         </is>
       </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -717,6 +795,9 @@
           <t>5110 Direct Labor - Wages</t>
         </is>
       </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -724,6 +805,9 @@
           <t>51110-000 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -731,6 +815,9 @@
           <t>5130 Direct Labor - OT</t>
         </is>
       </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -738,6 +825,9 @@
           <t>5140 Direct Labor - PTO</t>
         </is>
       </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -745,6 +835,9 @@
           <t>5185 Direct Labor - Other Benefits</t>
         </is>
       </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -752,6 +845,9 @@
           <t>52101-000 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -759,6 +855,9 @@
           <t>5221 The TREAD Agency - DL Wages</t>
         </is>
       </c>
+      <c r="B34">
+        <v>15</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -766,6 +865,9 @@
           <t>53101-000 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B35">
+        <v>15</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -773,6 +875,9 @@
           <t>5503 Sales - Salary</t>
         </is>
       </c>
+      <c r="B36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -780,6 +885,9 @@
           <t>60001 Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B37">
+        <v>15</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -787,6 +895,9 @@
           <t>60002 Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B38">
+        <v>15</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -794,6 +905,9 @@
           <t>6001 Wages</t>
         </is>
       </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -801,6 +915,9 @@
           <t>60010 Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B40">
+        <v>15</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -808,6 +925,9 @@
           <t>60011-000 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B41">
+        <v>15</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -815,6 +935,9 @@
           <t>6002 Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -822,6 +945,9 @@
           <t>60020 Wages</t>
         </is>
       </c>
+      <c r="B43">
+        <v>15</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -829,6 +955,9 @@
           <t>6003 Indirect Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B44">
+        <v>15</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -836,6 +965,9 @@
           <t>6021 Employee PR - Wages</t>
         </is>
       </c>
+      <c r="B45">
+        <v>15</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -843,6 +975,9 @@
           <t>6021 Employee Wages</t>
         </is>
       </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -850,6 +985,9 @@
           <t>6022 Wages</t>
         </is>
       </c>
+      <c r="B47">
+        <v>15</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -857,6 +995,9 @@
           <t>6030 Wages</t>
         </is>
       </c>
+      <c r="B48">
+        <v>15</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -864,6 +1005,9 @@
           <t>6100 Indirect Salaries &amp; Benefits</t>
         </is>
       </c>
+      <c r="B49">
+        <v>15</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -871,6 +1015,9 @@
           <t>6101 Employee PR - Wages</t>
         </is>
       </c>
+      <c r="B50">
+        <v>15</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -878,6 +1025,9 @@
           <t>6101.2 Wages - Social Media Ma...</t>
         </is>
       </c>
+      <c r="B51">
+        <v>15</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -885,6 +1035,9 @@
           <t>6101.3 Wages - Social Media Ad...</t>
         </is>
       </c>
+      <c r="B52">
+        <v>15</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -892,6 +1045,9 @@
           <t>6101.4 Wages - SEM</t>
         </is>
       </c>
+      <c r="B53">
+        <v>15</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -899,6 +1055,9 @@
           <t>6101.5 Wages - Sales</t>
         </is>
       </c>
+      <c r="B54">
+        <v>15</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -906,6 +1065,9 @@
           <t>6101.6 Wages - Video</t>
         </is>
       </c>
+      <c r="B55">
+        <v>15</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -913,6 +1075,9 @@
           <t>6110 Employee PR - Wages</t>
         </is>
       </c>
+      <c r="B56">
+        <v>15</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -920,6 +1085,9 @@
           <t>6356 Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B57">
+        <v>15</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -927,6 +1095,9 @@
           <t>6401 Employee Wages</t>
         </is>
       </c>
+      <c r="B58">
+        <v>15</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -934,6 +1105,9 @@
           <t>64100 Wages</t>
         </is>
       </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -941,6 +1115,9 @@
           <t>6451 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B60">
+        <v>15</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -948,6 +1125,9 @@
           <t>65101-000 Salaries and Wages</t>
         </is>
       </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -955,91 +1135,145 @@
           <t>6551 Salaries &amp; Wages</t>
         </is>
       </c>
+      <c r="B62">
+        <v>15</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
           <t>6701 Salaries &amp; Wages</t>
         </is>
+      </c>
+      <c r="B63">
+        <v>15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
         <v>0</v>
       </c>
+      <c r="B64">
+        <v>15</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
         <v>1</v>
       </c>
+      <c r="B65">
+        <v>15</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
         <v>2</v>
       </c>
+      <c r="B66">
+        <v>15</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
         <v>3</v>
       </c>
+      <c r="B67">
+        <v>15</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
         <v>4</v>
       </c>
+      <c r="B68">
+        <v>15</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
         <v>5</v>
       </c>
+      <c r="B69">
+        <v>15</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
         <v>6</v>
       </c>
+      <c r="B70">
+        <v>15</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
         <v>7</v>
       </c>
+      <c r="B71">
+        <v>15</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
         <v>8</v>
       </c>
+      <c r="B72">
+        <v>15</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
         <v>9</v>
       </c>
+      <c r="B73">
+        <v>15</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
         <v>10</v>
       </c>
+      <c r="B74">
+        <v>15</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
         <v>11</v>
       </c>
+      <c r="B75">
+        <v>15</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
         <v>12</v>
       </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
         <v>13</v>
       </c>
+      <c r="B77">
+        <v>15</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
         <v>14</v>
       </c>
+      <c r="B78">
+        <v>15</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79">
         <v>15</v>
       </c>
     </row>
@@ -1047,35 +1281,56 @@
       <c r="A80" t="s">
         <v>16</v>
       </c>
+      <c r="B80">
+        <v>15</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
         <v>17</v>
       </c>
+      <c r="B81">
+        <v>15</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
         <v>18</v>
       </c>
+      <c r="B82">
+        <v>15</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
         <v>19</v>
       </c>
+      <c r="B83">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
         <v>20</v>
       </c>
+      <c r="B84">
+        <v>15</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
         <v>21</v>
       </c>
+      <c r="B85">
+        <v>15</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
         <v>22</v>
+      </c>
+      <c r="B86">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1084,15 +1339,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1123,6 +1378,9 @@
           <t>1-65550 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1130,6 +1388,9 @@
           <t>2202 CA PIT / SDI</t>
         </is>
       </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1137,6 +1398,9 @@
           <t>2202 Federal Taxes (941/943/944)</t>
         </is>
       </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1144,6 +1408,9 @@
           <t>2203 CA PIT / SDI</t>
         </is>
       </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1151,6 +1418,9 @@
           <t>2203 CA SUI / ETT</t>
         </is>
       </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1158,6 +1428,9 @@
           <t>2203 Federal Taxes (941/944)</t>
         </is>
       </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1165,6 +1438,9 @@
           <t>2203 Federal Unemployment (940)</t>
         </is>
       </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1172,6 +1448,9 @@
           <t>2204 CA SUI / ETT</t>
         </is>
       </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1179,6 +1458,9 @@
           <t>2204 Federal Taxes (941/943/944)</t>
         </is>
       </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1186,6 +1468,9 @@
           <t>2204 Federal Unemployment (940)</t>
         </is>
       </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1193,6 +1478,9 @@
           <t>2205 Federal Unemployment (940)</t>
         </is>
       </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1200,6 +1488,9 @@
           <t>2206 Federal Taxes (941/944)</t>
         </is>
       </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1207,6 +1498,9 @@
           <t>2207 Federal Unemployment (940)</t>
         </is>
       </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1214,6 +1508,9 @@
           <t>2207 Payroll Tax Liabilities</t>
         </is>
       </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1221,6 +1518,9 @@
           <t>2220 Payroll taxes payable</t>
         </is>
       </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1228,6 +1528,9 @@
           <t>22200-003 Payroll tax paya...</t>
         </is>
       </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1235,6 +1538,9 @@
           <t>2311 CA PIT / SDI</t>
         </is>
       </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1242,6 +1548,9 @@
           <t>2312 CA SUI / ETT</t>
         </is>
       </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1249,6 +1558,9 @@
           <t>2313 Federal Taxes (941/944)</t>
         </is>
       </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1256,6 +1568,9 @@
           <t>2315 Payroll Taxes Employee</t>
         </is>
       </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1263,6 +1578,9 @@
           <t>2401 CA PIT / SDI</t>
         </is>
       </c>
+      <c r="B22">
+        <v>15</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1270,6 +1588,9 @@
           <t>2402 ADP Payroll Tax Withheld</t>
         </is>
       </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1277,6 +1598,9 @@
           <t>2402 CA SUI / ETT</t>
         </is>
       </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1284,6 +1608,9 @@
           <t>2403 Federal Taxes (941/...</t>
         </is>
       </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1291,6 +1618,9 @@
           <t>24031 CA PIT / SDI</t>
         </is>
       </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1298,6 +1628,9 @@
           <t>24041 CA SUI / ETT</t>
         </is>
       </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1305,6 +1638,9 @@
           <t>2405 Accured Payroll Taxes</t>
         </is>
       </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1312,6 +1648,9 @@
           <t>24051 Federal Taxes (941/944)</t>
         </is>
       </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1319,6 +1658,9 @@
           <t>24061 Federal Unemployment (940)</t>
         </is>
       </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1326,6 +1668,9 @@
           <t>3-65550 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1333,6 +1678,9 @@
           <t>3103 Federal Taxes</t>
         </is>
       </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1340,6 +1688,9 @@
           <t>4-65550 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1347,6 +1698,9 @@
           <t>5002 Direct Labor - Taxes</t>
         </is>
       </c>
+      <c r="B34">
+        <v>15</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1354,6 +1708,9 @@
           <t>5002 Direct Payroll Taxes</t>
         </is>
       </c>
+      <c r="B35">
+        <v>15</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1361,6 +1718,9 @@
           <t>5005 Direct Support Payroll Taxes</t>
         </is>
       </c>
+      <c r="B36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1368,6 +1728,9 @@
           <t>5102 Direct Labor PR - Taxes</t>
         </is>
       </c>
+      <c r="B37">
+        <v>15</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1375,6 +1738,9 @@
           <t>5102 Direct Payroll Taxes</t>
         </is>
       </c>
+      <c r="B38">
+        <v>15</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1382,6 +1748,9 @@
           <t>51120-000 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1389,6 +1758,9 @@
           <t>5120 Direct Labor - Taxes</t>
         </is>
       </c>
+      <c r="B40">
+        <v>15</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1396,6 +1768,9 @@
           <t>52103-000 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B41">
+        <v>15</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1403,6 +1778,9 @@
           <t>53103-000 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1410,6 +1788,9 @@
           <t>5320 Payroll Taxes - Direct</t>
         </is>
       </c>
+      <c r="B43">
+        <v>15</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1417,6 +1798,9 @@
           <t>60003 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B44">
+        <v>15</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1424,6 +1808,9 @@
           <t>60005 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B45">
+        <v>15</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1431,6 +1818,9 @@
           <t>60014-000 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1438,6 +1828,9 @@
           <t>6002 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B47">
+        <v>15</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1445,6 +1838,9 @@
           <t>60020 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B48">
+        <v>15</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1452,6 +1848,9 @@
           <t>60030 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B49">
+        <v>15</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1459,6 +1858,9 @@
           <t>6007 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B50">
+        <v>15</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1466,6 +1868,9 @@
           <t>6022 Employee PR - Taxes</t>
         </is>
       </c>
+      <c r="B51">
+        <v>15</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1473,6 +1878,9 @@
           <t>6022 Employee Taxes</t>
         </is>
       </c>
+      <c r="B52">
+        <v>15</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1480,6 +1888,9 @@
           <t>6023 Payroll Tax Expense</t>
         </is>
       </c>
+      <c r="B53">
+        <v>15</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1487,6 +1898,9 @@
           <t>6102 Employee PR - Taxes</t>
         </is>
       </c>
+      <c r="B54">
+        <v>15</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1494,6 +1908,9 @@
           <t>6120 Employee PR - Taxes</t>
         </is>
       </c>
+      <c r="B55">
+        <v>15</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1501,6 +1918,9 @@
           <t>6354 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B56">
+        <v>15</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1508,6 +1928,9 @@
           <t>6402 Employee Taxes</t>
         </is>
       </c>
+      <c r="B57">
+        <v>15</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1515,6 +1938,9 @@
           <t>6452 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B58">
+        <v>15</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1522,6 +1948,9 @@
           <t>65102-000 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1529,12 +1958,18 @@
           <t>6703 Payroll Taxes</t>
         </is>
       </c>
+      <c r="B60">
+        <v>15</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
           <t>62000 Business Licenses and Taxes</t>
         </is>
+      </c>
+      <c r="B61">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1543,15 +1978,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1582,6 +2017,9 @@
           <t>1-65510 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1589,6 +2027,9 @@
           <t>3-65510 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1596,6 +2037,9 @@
           <t>4-65510 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1603,6 +2047,9 @@
           <t>60004 Payroll Processing Fee</t>
         </is>
       </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1610,6 +2057,9 @@
           <t>60005 Payroll Fee</t>
         </is>
       </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1617,6 +2067,9 @@
           <t>60006 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1624,6 +2077,9 @@
           <t>6004 Payroll Fees</t>
         </is>
       </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1631,6 +2087,9 @@
           <t>6006 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1638,6 +2097,9 @@
           <t>60060 Payroll Fees</t>
         </is>
       </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1645,6 +2107,9 @@
           <t>6008 Payroll Fees</t>
         </is>
       </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1652,6 +2117,9 @@
           <t>6009 401K Processing Fee</t>
         </is>
       </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1659,6 +2127,9 @@
           <t>6025 Payroll Fees</t>
         </is>
       </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1666,6 +2137,9 @@
           <t>6030 Payroll Fees</t>
         </is>
       </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1673,6 +2147,9 @@
           <t>6030 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1680,6 +2157,9 @@
           <t>6031 401K Processing Fee</t>
         </is>
       </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1687,6 +2167,9 @@
           <t>6032 Payroll Fees - HSA</t>
         </is>
       </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1694,6 +2177,9 @@
           <t>6110 Payroll Fees</t>
         </is>
       </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1701,6 +2187,9 @@
           <t>6200 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1708,6 +2197,9 @@
           <t>6355 Payroll Fees</t>
         </is>
       </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1715,6 +2207,9 @@
           <t>6403 Payroll Fees</t>
         </is>
       </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1722,6 +2217,9 @@
           <t>6407 ADP Payroll Fees</t>
         </is>
       </c>
+      <c r="B22">
+        <v>15</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1729,6 +2227,9 @@
           <t>6453 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1736,6 +2237,9 @@
           <t>65108-000 Payroll Processing Fees</t>
         </is>
       </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1743,12 +2247,18 @@
           <t>6558 Payroll Processing Fee</t>
         </is>
       </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>6708 Payroll Processing Fees</t>
         </is>
+      </c>
+      <c r="B26">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1757,15 +2267,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1796,6 +2306,9 @@
           <t>1-14040 Software</t>
         </is>
       </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1803,6 +2316,9 @@
           <t>1-61000 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1810,6 +2326,9 @@
           <t>12700-000 Software Development Costs</t>
         </is>
       </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1817,6 +2336,9 @@
           <t>13005 Software</t>
         </is>
       </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1824,6 +2346,9 @@
           <t>1301 Computer Software</t>
         </is>
       </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1831,6 +2356,9 @@
           <t>13020 Computer &amp; Software</t>
         </is>
       </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1838,6 +2366,9 @@
           <t>1311 Software - Fixed asset</t>
         </is>
       </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1845,6 +2376,9 @@
           <t>1320 Computers &amp; Software</t>
         </is>
       </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1852,6 +2386,9 @@
           <t>1401 Computer Software</t>
         </is>
       </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1859,6 +2396,9 @@
           <t>1501 Software Development</t>
         </is>
       </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1866,6 +2406,9 @@
           <t>2-61000 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1873,6 +2416,9 @@
           <t>3-61000 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1880,6 +2426,9 @@
           <t>4-64600 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1887,6 +2436,9 @@
           <t>40000 Membership Dues</t>
         </is>
       </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1894,6 +2446,9 @@
           <t>40100-000 Membership Dues</t>
         </is>
       </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1901,6 +2456,9 @@
           <t>40100-008 Community Subscription</t>
         </is>
       </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1908,6 +2466,9 @@
           <t>50020 Software and Tools Subsc...</t>
         </is>
       </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1915,6 +2476,9 @@
           <t>5003 Software &amp; Apps - COGS</t>
         </is>
       </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1922,6 +2486,9 @@
           <t>5004 SaaS Software</t>
         </is>
       </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1929,6 +2496,9 @@
           <t>5004 Software &amp; App COGS</t>
         </is>
       </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1936,6 +2506,9 @@
           <t>5005 Software &amp; App COGS</t>
         </is>
       </c>
+      <c r="B22">
+        <v>15</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1943,6 +2516,9 @@
           <t>5040 Software COGS - Apps &amp; Other</t>
         </is>
       </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1950,6 +2526,9 @@
           <t>5200 Production Software</t>
         </is>
       </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1957,6 +2536,9 @@
           <t>5210 Software &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1964,6 +2546,9 @@
           <t>6004 Office Supplies &amp; Software</t>
         </is>
       </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1971,6 +2556,9 @@
           <t>60101-000 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1978,6 +2566,9 @@
           <t>6040 Dues &amp; Membership</t>
         </is>
       </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1985,6 +2576,9 @@
           <t>6041 Douglas Elliman Dues</t>
         </is>
       </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1992,6 +2586,9 @@
           <t>6045 Other Dues &amp; Memberships</t>
         </is>
       </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1999,6 +2596,9 @@
           <t>60500 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2006,6 +2606,9 @@
           <t>6052 Association Dues</t>
         </is>
       </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2013,6 +2616,9 @@
           <t>6055 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2020,6 +2626,9 @@
           <t>6063 Software Expenses</t>
         </is>
       </c>
+      <c r="B34">
+        <v>15</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2027,6 +2636,9 @@
           <t>6100 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B35">
+        <v>15</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2034,6 +2646,9 @@
           <t>6101 Computer Software</t>
         </is>
       </c>
+      <c r="B36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2041,6 +2656,9 @@
           <t>6101 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B37">
+        <v>15</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2048,6 +2666,9 @@
           <t>6130 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B38">
+        <v>15</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2055,6 +2676,9 @@
           <t>6151 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2062,6 +2686,9 @@
           <t>6152 Software &amp; Applications</t>
         </is>
       </c>
+      <c r="B40">
+        <v>15</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2069,6 +2696,9 @@
           <t>6153 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B41">
+        <v>15</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2076,6 +2706,9 @@
           <t>6155 Office Software</t>
         </is>
       </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2083,6 +2716,9 @@
           <t>6155 Software &amp; Apps</t>
         </is>
       </c>
+      <c r="B43">
+        <v>15</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2090,6 +2726,9 @@
           <t>61550 Software &amp; Apps</t>
         </is>
       </c>
+      <c r="B44">
+        <v>15</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2097,6 +2736,9 @@
           <t>6158 Software &amp; Apps</t>
         </is>
       </c>
+      <c r="B45">
+        <v>15</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2104,6 +2746,9 @@
           <t>6158 Software &amp; apps</t>
         </is>
       </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2111,6 +2756,9 @@
           <t>6200 Computer Software &amp; Inter...</t>
         </is>
       </c>
+      <c r="B47">
+        <v>15</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2118,6 +2766,9 @@
           <t>6200 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B48">
+        <v>15</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2125,6 +2776,9 @@
           <t>6201 Dues &amp; Subscription</t>
         </is>
       </c>
+      <c r="B49">
+        <v>15</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2132,6 +2786,9 @@
           <t>6203 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B50">
+        <v>15</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2139,6 +2796,9 @@
           <t>6204 Software Subscriptions</t>
         </is>
       </c>
+      <c r="B51">
+        <v>15</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2146,6 +2806,9 @@
           <t>6205 Software &amp; Computer Expen...</t>
         </is>
       </c>
+      <c r="B52">
+        <v>15</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2153,6 +2816,9 @@
           <t>6206 Software &amp; Apps</t>
         </is>
       </c>
+      <c r="B53">
+        <v>15</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2160,6 +2826,9 @@
           <t>6215 Computer Software</t>
         </is>
       </c>
+      <c r="B54">
+        <v>15</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2167,6 +2836,9 @@
           <t>62275 Dues &amp; Subscription</t>
         </is>
       </c>
+      <c r="B55">
+        <v>15</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2174,6 +2846,9 @@
           <t>6250 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B56">
+        <v>15</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2181,6 +2856,9 @@
           <t>62500 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B57">
+        <v>15</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2188,6 +2866,9 @@
           <t>62500 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B58">
+        <v>15</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2195,6 +2876,9 @@
           <t>62500 Office Supplies &amp; Software</t>
         </is>
       </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2202,6 +2886,9 @@
           <t>6255 Subscriptions</t>
         </is>
       </c>
+      <c r="B60">
+        <v>15</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2209,6 +2896,9 @@
           <t>6275 Software, Apps, Subscriptions</t>
         </is>
       </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2216,6 +2906,9 @@
           <t>6300 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B62">
+        <v>15</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2223,6 +2916,9 @@
           <t>6300 Memberships &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B63">
+        <v>15</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2230,6 +2926,9 @@
           <t>6300 Systems &amp; Software</t>
         </is>
       </c>
+      <c r="B64">
+        <v>15</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2237,6 +2936,9 @@
           <t>6301 Software &amp; Applications</t>
         </is>
       </c>
+      <c r="B65">
+        <v>15</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2244,6 +2946,9 @@
           <t>6302 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B66">
+        <v>15</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2251,6 +2956,9 @@
           <t>63031 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B67">
+        <v>15</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2258,6 +2966,9 @@
           <t>6307 Software &amp; Apps</t>
         </is>
       </c>
+      <c r="B68">
+        <v>15</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2265,6 +2976,9 @@
           <t>6352 Apps &amp; Software</t>
         </is>
       </c>
+      <c r="B69">
+        <v>15</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2272,6 +2986,9 @@
           <t>6353 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B70">
+        <v>15</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2279,6 +2996,9 @@
           <t>6401 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B71">
+        <v>15</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2286,6 +3006,9 @@
           <t>6404 Software Expenses</t>
         </is>
       </c>
+      <c r="B72">
+        <v>15</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2293,6 +3016,9 @@
           <t>6405 Software</t>
         </is>
       </c>
+      <c r="B73">
+        <v>15</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2300,6 +3026,9 @@
           <t>6450 Office Supplies &amp; Software</t>
         </is>
       </c>
+      <c r="B74">
+        <v>15</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2307,6 +3036,9 @@
           <t>65270-000 Dues and Subscriptions</t>
         </is>
       </c>
+      <c r="B75">
+        <v>15</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2314,6 +3046,9 @@
           <t>6600 Office Supplies &amp; Software</t>
         </is>
       </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2321,6 +3056,9 @@
           <t>6715 Software Expense</t>
         </is>
       </c>
+      <c r="B77">
+        <v>15</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2328,6 +3066,9 @@
           <t>6903 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B78">
+        <v>15</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2335,12 +3076,18 @@
           <t>69030 Dues &amp; Subscriptions</t>
         </is>
       </c>
+      <c r="B79">
+        <v>15</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
           <t>69030 Dues and Subscriptions</t>
         </is>
+      </c>
+      <c r="B80">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2349,15 +3096,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col customWidth="true" max="1" min="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2388,6 +3135,9 @@
           <t>1-67000 Telephone Expense</t>
         </is>
       </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2395,6 +3145,9 @@
           <t>1-67700 Utilities</t>
         </is>
       </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2402,6 +3155,9 @@
           <t>1303 Phone Hardware</t>
         </is>
       </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2409,6 +3165,9 @@
           <t>3-61750 Computer and Internet Expenses</t>
         </is>
       </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2416,6 +3175,9 @@
           <t>3-67000 Telephone Expense</t>
         </is>
       </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2423,6 +3185,9 @@
           <t>3-67700 Utilities</t>
         </is>
       </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2430,6 +3195,9 @@
           <t>4-67000 Telephone Expense</t>
         </is>
       </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2437,6 +3205,9 @@
           <t>4-67700 Utilities</t>
         </is>
       </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2444,6 +3215,9 @@
           <t>5511 Cell Phone Expense - Sales</t>
         </is>
       </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2451,6 +3225,9 @@
           <t>6045 Computer and Internet Expen...</t>
         </is>
       </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2458,6 +3235,9 @@
           <t>6062 Utilities</t>
         </is>
       </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2465,6 +3245,9 @@
           <t>6063 Telephone</t>
         </is>
       </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2472,6 +3255,9 @@
           <t>6064 Internet Expense</t>
         </is>
       </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2479,6 +3265,9 @@
           <t>6065 Utilities</t>
         </is>
       </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2486,6 +3275,9 @@
           <t>6100 Computer and Internet</t>
         </is>
       </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2493,6 +3285,9 @@
           <t>6101 Gas</t>
         </is>
       </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2500,6 +3295,9 @@
           <t>6103 Phone service</t>
         </is>
       </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2507,6 +3305,9 @@
           <t>6115 Utilities</t>
         </is>
       </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2514,6 +3315,9 @@
           <t>6117 Internet &amp; Telephone</t>
         </is>
       </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2521,6 +3325,9 @@
           <t>6154 Electric &amp; Gas</t>
         </is>
       </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2528,6 +3335,9 @@
           <t>6155 Phone &amp; Internet Expenses</t>
         </is>
       </c>
+      <c r="B22">
+        <v>15</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2535,6 +3345,9 @@
           <t>61600 Utilities</t>
         </is>
       </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2542,6 +3355,9 @@
           <t>61700 Computer and Internet Expe...</t>
         </is>
       </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2549,6 +3365,9 @@
           <t>61700 Telephone Expense</t>
         </is>
       </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2556,6 +3375,9 @@
           <t>6200 Computer and Internet Expenses</t>
         </is>
       </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2563,6 +3385,9 @@
           <t>62000 Office &amp; Utility Expenses</t>
         </is>
       </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2570,6 +3395,9 @@
           <t>6203 Phone/Internet</t>
         </is>
       </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2577,6 +3405,9 @@
           <t>62030 Gas/Mileage</t>
         </is>
       </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2584,6 +3415,9 @@
           <t>6204 Internet &amp; Telephone Expe...</t>
         </is>
       </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2591,6 +3425,9 @@
           <t>62051 Utilities</t>
         </is>
       </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2598,6 +3435,9 @@
           <t>6207 Vehicle Gas &amp; Fuel</t>
         </is>
       </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2605,6 +3445,9 @@
           <t>6225 Utilities</t>
         </is>
       </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2612,6 +3455,9 @@
           <t>6230 Cell Phone</t>
         </is>
       </c>
+      <c r="B34">
+        <v>15</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2619,6 +3465,9 @@
           <t>6231 Internet</t>
         </is>
       </c>
+      <c r="B35">
+        <v>15</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2626,6 +3475,9 @@
           <t>6233 Phone Service</t>
         </is>
       </c>
+      <c r="B36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2633,6 +3485,9 @@
           <t>6256 Telephone &amp; Internet</t>
         </is>
       </c>
+      <c r="B37">
+        <v>15</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2640,6 +3495,9 @@
           <t>6257 Utilities</t>
         </is>
       </c>
+      <c r="B38">
+        <v>15</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2647,6 +3505,9 @@
           <t>62850 Utilities</t>
         </is>
       </c>
+      <c r="B39">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2654,6 +3515,9 @@
           <t>6301 Gas</t>
         </is>
       </c>
+      <c r="B40">
+        <v>15</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2661,6 +3525,9 @@
           <t>63020 Gas / Electric Charging</t>
         </is>
       </c>
+      <c r="B41">
+        <v>15</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2668,6 +3535,9 @@
           <t>6308 Telephone &amp; Internet</t>
         </is>
       </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2675,6 +3545,9 @@
           <t>6366 Telephone</t>
         </is>
       </c>
+      <c r="B43">
+        <v>15</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2682,6 +3555,9 @@
           <t>6367 Utilities</t>
         </is>
       </c>
+      <c r="B44">
+        <v>15</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2689,6 +3565,9 @@
           <t>6375 Utilities</t>
         </is>
       </c>
+      <c r="B45">
+        <v>15</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2696,6 +3575,9 @@
           <t>64020 Utilities</t>
         </is>
       </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2703,6 +3585,9 @@
           <t>6403 Internet</t>
         </is>
       </c>
+      <c r="B47">
+        <v>15</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2710,6 +3595,9 @@
           <t>64030 Telephone</t>
         </is>
       </c>
+      <c r="B48">
+        <v>15</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2717,6 +3605,9 @@
           <t>6404 Telephone</t>
         </is>
       </c>
+      <c r="B49">
+        <v>15</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2724,6 +3615,9 @@
           <t>64040 Internet</t>
         </is>
       </c>
+      <c r="B50">
+        <v>15</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2731,6 +3625,9 @@
           <t>65240-001 Telephone Expense</t>
         </is>
       </c>
+      <c r="B51">
+        <v>15</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2738,6 +3635,9 @@
           <t>6653 Electricity</t>
         </is>
       </c>
+      <c r="B52">
+        <v>15</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2745,6 +3645,9 @@
           <t>6654 Internet &amp; TV Services</t>
         </is>
       </c>
+      <c r="B53">
+        <v>15</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2752,6 +3655,9 @@
           <t>6655 Other Utilities</t>
         </is>
       </c>
+      <c r="B54">
+        <v>15</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2759,6 +3665,9 @@
           <t>6750 Telephone Expense</t>
         </is>
       </c>
+      <c r="B55">
+        <v>15</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2766,6 +3675,9 @@
           <t>6800 Telephone Expense</t>
         </is>
       </c>
+      <c r="B56">
+        <v>15</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2773,6 +3685,9 @@
           <t>6800 Utilities</t>
         </is>
       </c>
+      <c r="B57">
+        <v>15</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2780,6 +3695,9 @@
           <t>6801 Cable &amp; Internet</t>
         </is>
       </c>
+      <c r="B58">
+        <v>15</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2787,6 +3705,9 @@
           <t>6801 Gas &amp; Car Charge</t>
         </is>
       </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2794,6 +3715,9 @@
           <t>6801 Gas &amp; Fuel</t>
         </is>
       </c>
+      <c r="B60">
+        <v>15</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2801,6 +3725,9 @@
           <t>6806 Telephone</t>
         </is>
       </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2808,6 +3735,9 @@
           <t>68100 Telephone Expense</t>
         </is>
       </c>
+      <c r="B62">
+        <v>15</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2815,6 +3745,9 @@
           <t>6850 Telephone</t>
         </is>
       </c>
+      <c r="B63">
+        <v>15</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2822,6 +3755,9 @@
           <t>68600 Utilities</t>
         </is>
       </c>
+      <c r="B64">
+        <v>15</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2829,12 +3765,18 @@
           <t>6900 Utilities</t>
         </is>
       </c>
+      <c r="B65">
+        <v>15</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
           <t>6950 Utilities</t>
         </is>
+      </c>
+      <c r="B66">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
